--- a/docs/Lab02/Lab02_BBT_TCs_Form1.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UBB2\an3\VVSS\lab2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UBB2\an3\VVSS\MyDrinkShop-VVSS\docs\Lab02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E59D19-2B56-44DF-84B5-85F01C3D71AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBE349C-0406-4C4B-B00A-E30F20B7F0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -46,6 +46,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Author:
@@ -71,6 +72,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Author:
@@ -85,6 +87,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Author:
@@ -98,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="144">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -145,18 +148,22 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
+    <t>Observații</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
+  </si>
+  <si>
+    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>F01.</t>
     </r>
@@ -165,114 +172,142 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
+      <t xml:space="preserve"> adăugarea unui produs nou (id, nume, pret, categorie,tip);</t>
     </r>
   </si>
   <si>
-    <t>Observații</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
-    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
-  </si>
-  <si>
-    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
-  </si>
-  <si>
-    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Exemplu: Parametrii </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> şi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">; Condiţii pentru aceşti parametri de intrare: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0066CC"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
-    </r>
+    <t>EC Identification</t>
+  </si>
+  <si>
+    <t>EC-based TCs</t>
+  </si>
+  <si>
+    <t>No. EC</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Valid EC</t>
+  </si>
+  <si>
+    <t>Non-valid EC</t>
+  </si>
+  <si>
+    <t>No. TCxx_EC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>input data</t>
+  </si>
+  <si>
+    <t>output data</t>
+  </si>
+  <si>
+    <t>pret is double</t>
+  </si>
+  <si>
+    <t>categorie</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>BVA Condition</t>
+  </si>
+  <si>
+    <t>BVA Condition-based TCs</t>
+  </si>
+  <si>
+    <t>Crt. No.</t>
+  </si>
+  <si>
+    <t>No TCxx_BVA</t>
+  </si>
+  <si>
+    <t>BVA condition</t>
+  </si>
+  <si>
+    <t>Correlated TC</t>
+  </si>
+  <si>
+    <t>Executable</t>
+  </si>
+  <si>
+    <t>TC3_EC</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>BBT TCs</t>
+  </si>
+  <si>
+    <t>Final        TC No.</t>
+  </si>
+  <si>
+    <t>Req. ID</t>
+  </si>
+  <si>
+    <t>ECP TCs</t>
+  </si>
+  <si>
+    <t>BVA TCs</t>
+  </si>
+  <si>
+    <t>actual result</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>TC1_ECP</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TC3_ECP</t>
+  </si>
+  <si>
+    <t>TC5_ECP</t>
+  </si>
+  <si>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Re-testing</t>
+  </si>
+  <si>
+    <t>Regression Testing</t>
+  </si>
+  <si>
+    <t>#TCs to be run</t>
   </si>
   <si>
     <r>
@@ -281,157 +316,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui produs nou (id, nume, pret, categorie,tip);</t>
-    </r>
-  </si>
-  <si>
-    <t>EC Identification</t>
-  </si>
-  <si>
-    <t>EC-based TCs</t>
-  </si>
-  <si>
-    <t>No. EC</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Valid EC</t>
-  </si>
-  <si>
-    <t>Non-valid EC</t>
-  </si>
-  <si>
-    <t>No. TCxx_EC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>input data</t>
-  </si>
-  <si>
-    <t>output data</t>
-  </si>
-  <si>
-    <t>pret is double</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>BVA Condition</t>
-  </si>
-  <si>
-    <t>BVA Condition-based TCs</t>
-  </si>
-  <si>
-    <t>Crt. No.</t>
-  </si>
-  <si>
-    <t>No TCxx_BVA</t>
-  </si>
-  <si>
-    <t>BVA condition</t>
-  </si>
-  <si>
-    <t>Correlated TC</t>
-  </si>
-  <si>
-    <t>Executable</t>
-  </si>
-  <si>
-    <t>TC3_EC</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>BBT TCs</t>
-  </si>
-  <si>
-    <t>Final        TC No.</t>
-  </si>
-  <si>
-    <t>Req. ID</t>
-  </si>
-  <si>
-    <t>ECP TCs</t>
-  </si>
-  <si>
-    <t>BVA TCs</t>
-  </si>
-  <si>
-    <t>actual result</t>
-  </si>
-  <si>
-    <t>F01</t>
-  </si>
-  <si>
-    <t>TC1_ECP</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TC3_ECP</t>
-  </si>
-  <si>
-    <t>TC5_ECP</t>
-  </si>
-  <si>
-    <t>TC3_BVA</t>
-  </si>
-  <si>
-    <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Debugging</t>
-  </si>
-  <si>
-    <t>Re-testing</t>
-  </si>
-  <si>
-    <t>Regression Testing</t>
-  </si>
-  <si>
-    <t>#TCs to be run</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs </t>
     </r>
@@ -441,6 +326,7 @@
         <sz val="11"/>
         <color rgb="FF008000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>passed</t>
     </r>
@@ -452,6 +338,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs    </t>
     </r>
@@ -461,6 +348,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>failed</t>
     </r>
@@ -481,6 +369,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs </t>
     </r>
@@ -490,6 +379,7 @@
         <sz val="11"/>
         <color rgb="FF008000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>passed</t>
     </r>
@@ -501,6 +391,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs    </t>
     </r>
@@ -510,6 +401,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>failed</t>
     </r>
@@ -521,6 +413,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs </t>
     </r>
@@ -530,6 +423,7 @@
         <sz val="11"/>
         <color rgb="FF008000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>passed</t>
     </r>
@@ -541,6 +435,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">#TCs    </t>
     </r>
@@ -550,6 +445,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>failed</t>
     </r>
@@ -754,52 +650,28 @@
   </si>
   <si>
     <t>TC13_BVA</t>
+  </si>
+  <si>
+    <t>1. Magazin bauturi</t>
+  </si>
+  <si>
+    <t>Se doreste adaugarea unui produs</t>
+  </si>
+  <si>
+    <t>addProduct(int id, String name,double price, CategoryProduct category, TypeProduct type): void</t>
+  </si>
+  <si>
+    <t>2. Metoda este definită la nivelul repository</t>
+  </si>
+  <si>
+    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora =&gt; id si pret</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Candara"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,64 +681,113 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Courier New"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF31859B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF31859B"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF0066CC"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0066CC"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1595,371 +1516,371 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="42" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="37" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="37" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="42" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="37" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="37" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -2199,12 +2120,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="94"/>
       <c r="H1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2212,11 +2133,11 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H3" s="3"/>
@@ -2295,24 +2216,24 @@
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
-        <v>15</v>
+      <c r="B14" s="163" t="s">
+        <v>139</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
-        <v>16</v>
+      <c r="B15" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
-        <v>17</v>
+      <c r="B16" s="163" t="s">
+        <v>92</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -2325,27 +2246,27 @@
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="8" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2362,7 +2283,7 @@
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -2379,21 +2300,19 @@
     </row>
     <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
-      <c r="B24" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
     </row>
     <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3389,7 +3308,7 @@
   <sheetPr>
     <tabColor rgb="FFFBD4B4"/>
   </sheetPr>
-  <dimension ref="B1:Q1000"/>
+  <dimension ref="B1:P1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -3411,386 +3330,386 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="42"/>
+      <c r="B3" s="153" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="94"/>
     </row>
     <row r="4" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42"/>
-      <c r="G5" s="96" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
+      <c r="B5" s="147" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="94"/>
+      <c r="G5" s="154" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
     </row>
     <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="155" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="12" t="s">
+    </row>
+    <row r="7" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="40">
+        <v>1</v>
+      </c>
+      <c r="C7" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D7" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="M7" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="99"/>
+      <c r="O7" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="98" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="100" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="86">
+      <c r="P7" s="68"/>
+    </row>
+    <row r="8" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="40">
+        <v>2</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="51">
         <v>1</v>
       </c>
-      <c r="C7" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="87" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="100" t="s">
+      <c r="H8" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="52">
+        <v>1</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="52">
+        <v>10</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="99"/>
+      <c r="O8" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="J7" s="100" t="s">
+      <c r="P8" s="62"/>
+    </row>
+    <row r="9" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="40">
+        <v>3</v>
+      </c>
+      <c r="C9" s="152"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="51">
+        <v>2</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="52">
+        <v>2</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="52">
+        <v>8</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="M9" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="N9" s="99"/>
+      <c r="O9" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="P9" s="62"/>
+    </row>
+    <row r="10" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="40">
+        <v>4</v>
+      </c>
+      <c r="C10" s="150" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="G10" s="54">
+        <v>3</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="55">
+        <v>0</v>
+      </c>
+      <c r="J10" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="100" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" s="100" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="99" t="s">
-        <v>84</v>
-      </c>
-      <c r="N7" s="97"/>
-      <c r="O7" s="127" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="128"/>
-    </row>
-    <row r="8" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="86">
-        <v>2</v>
-      </c>
-      <c r="C8" s="108"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="100">
+      <c r="K10" s="55">
+        <v>10</v>
+      </c>
+      <c r="L10" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N10" s="99"/>
+      <c r="O10" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" s="60"/>
+    </row>
+    <row r="11" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="40">
+        <v>5</v>
+      </c>
+      <c r="C11" s="152"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="48">
+        <v>4</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="49">
         <v>1</v>
       </c>
-      <c r="H8" s="101" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="101">
-        <v>1</v>
-      </c>
-      <c r="J8" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" s="101">
-        <v>10</v>
-      </c>
-      <c r="L8" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="M8" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="97"/>
-      <c r="O8" s="121" t="s">
-        <v>88</v>
-      </c>
-      <c r="P8" s="122"/>
-    </row>
-    <row r="9" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="86">
-        <v>3</v>
-      </c>
-      <c r="C9" s="109"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" s="100">
-        <v>2</v>
-      </c>
-      <c r="H9" s="101" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="101">
-        <v>2</v>
-      </c>
-      <c r="J9" s="101" t="s">
+      <c r="J11" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="49">
+        <v>0</v>
+      </c>
+      <c r="L11" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="M11" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N11" s="99"/>
+      <c r="O11" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="K9" s="101">
-        <v>8</v>
-      </c>
-      <c r="L9" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="M9" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="N9" s="97"/>
-      <c r="O9" s="121" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="122"/>
-    </row>
-    <row r="10" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="86">
-        <v>4</v>
-      </c>
-      <c r="C10" s="107" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="90"/>
-      <c r="G10" s="103">
-        <v>3</v>
-      </c>
-      <c r="H10" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" s="104">
-        <v>0</v>
-      </c>
-      <c r="J10" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="K10" s="104">
-        <v>10</v>
-      </c>
-      <c r="L10" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="N10" s="97"/>
-      <c r="O10" s="119" t="s">
-        <v>94</v>
-      </c>
-      <c r="P10" s="120"/>
-    </row>
-    <row r="11" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="86">
-        <v>5</v>
-      </c>
-      <c r="C11" s="109"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="94">
-        <v>4</v>
-      </c>
-      <c r="H11" s="95" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="95">
-        <v>1</v>
-      </c>
-      <c r="J11" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="K11" s="95">
-        <v>0</v>
-      </c>
-      <c r="L11" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="N11" s="97"/>
-      <c r="O11" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="P11" s="120"/>
+      <c r="P11" s="60"/>
     </row>
     <row r="12" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="86">
+      <c r="B12" s="40">
         <v>6</v>
       </c>
-      <c r="C12" s="88"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="G12" s="15">
         <v>5</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I12" s="16">
         <v>-3</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K12" s="16">
         <v>-34.200000000000003</v>
       </c>
-      <c r="L12" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="N12" s="97"/>
-      <c r="O12" s="119" t="s">
-        <v>98</v>
-      </c>
-      <c r="P12" s="120"/>
+      <c r="L12" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" s="99"/>
+      <c r="O12" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="60"/>
     </row>
     <row r="13" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13">
         <v>7</v>
       </c>
-      <c r="C13" s="85"/>
+      <c r="C13" s="148"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="G13" s="15">
         <v>6</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I13" s="16">
         <v>1</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K13" s="16">
         <v>10000</v>
       </c>
-      <c r="L13" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="M13" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13" s="97"/>
-      <c r="O13" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="P13" s="120"/>
+      <c r="L13" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N13" s="99"/>
+      <c r="O13" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" s="60"/>
     </row>
     <row r="14" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="13">
         <v>8</v>
       </c>
-      <c r="C14" s="48"/>
+      <c r="C14" s="125"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="G14" s="17">
         <v>7</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I14" s="16">
         <v>-3</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K14" s="16">
         <v>10001</v>
       </c>
-      <c r="L14" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14" s="97"/>
-      <c r="O14" s="119" t="s">
-        <v>98</v>
-      </c>
-      <c r="P14" s="120"/>
+      <c r="L14" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="99"/>
+      <c r="O14" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" s="60"/>
     </row>
     <row r="15" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13">
         <v>9</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>39</v>
+      <c r="C15" s="149" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="G15" s="17">
         <v>8</v>
       </c>
-      <c r="H15" s="162"/>
+      <c r="H15" s="91"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="126"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="66"/>
     </row>
     <row r="16" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="13">
         <v>10</v>
       </c>
-      <c r="C16" s="48"/>
+      <c r="C16" s="125"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="G16" s="17"/>
@@ -3799,17 +3718,17 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="124"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="63"/>
+      <c r="P16" s="64"/>
     </row>
     <row r="17" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="13">
         <v>11</v>
       </c>
-      <c r="C17" s="50" t="s">
-        <v>39</v>
+      <c r="C17" s="149" t="s">
+        <v>32</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -3819,16 +3738,16 @@
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="124"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="64"/>
     </row>
     <row r="18" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13">
         <v>12</v>
       </c>
-      <c r="C18" s="48"/>
+      <c r="C18" s="125"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="G18" s="17"/>
@@ -3837,14 +3756,14 @@
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="124"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="63"/>
+      <c r="P18" s="64"/>
     </row>
     <row r="19" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="3"/>
@@ -3852,16 +3771,16 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="124"/>
+      <c r="M19" s="144"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="63"/>
+      <c r="P19" s="64"/>
     </row>
     <row r="20" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F22" s="51"/>
-      <c r="G22" s="45"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="131"/>
     </row>
     <row r="23" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4843,13 +4762,15 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="G5:P5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="M18:N18"/>
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="M10:N10"/>
@@ -4860,15 +4781,13 @@
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="M17:N17"/>
     <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="G5:P5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4903,152 +4822,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="2" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="110" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="42"/>
+      <c r="B3" s="160" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="94"/>
     </row>
     <row r="4" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
+      <c r="B5" s="162" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="94"/>
       <c r="E5" s="19"/>
-      <c r="G5" s="96" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
+      <c r="G5" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
     </row>
     <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E6" s="20"/>
-      <c r="G6" s="98" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="98" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="112" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="113" t="s">
-        <v>35</v>
+      <c r="G6" s="155" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="155" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="155" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="97" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="161" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="58" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="50">
+      <c r="B7" s="149">
         <v>1</v>
       </c>
-      <c r="C7" s="54" t="s">
-        <v>127</v>
+      <c r="C7" s="157" t="s">
+        <v>120</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="100" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7" s="114" t="s">
-        <v>83</v>
-      </c>
-      <c r="N7" s="100" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="P7" s="115"/>
+        <v>122</v>
+      </c>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="43"/>
     </row>
     <row r="8" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
       <c r="D8" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G8" s="28">
         <v>1</v>
       </c>
-      <c r="H8" s="93">
+      <c r="H8" s="47">
         <v>1</v>
       </c>
-      <c r="I8" s="111" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="111" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="104">
+      <c r="I8" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="K8" s="55">
         <v>0</v>
       </c>
-      <c r="L8" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="M8" s="129">
+      <c r="L8" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="M8" s="69">
         <v>10</v>
       </c>
-      <c r="N8" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="O8" s="116" t="s">
-        <v>87</v>
-      </c>
-      <c r="P8" s="133" t="s">
-        <v>117</v>
+      <c r="N8" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" s="73" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
+      <c r="B9" s="156"/>
+      <c r="C9" s="156"/>
       <c r="D9" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G9" s="17">
         <v>2</v>
@@ -5057,35 +4976,35 @@
         <v>2</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="K9" s="101">
+        <v>107</v>
+      </c>
+      <c r="K9" s="52">
         <v>1</v>
       </c>
-      <c r="L9" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M9" s="130">
+      <c r="L9" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="70">
         <v>10</v>
       </c>
-      <c r="N9" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O9" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P9" s="89" t="s">
-        <v>88</v>
+      <c r="N9" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
       <c r="D10" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G10" s="11">
         <v>3</v>
@@ -5094,35 +5013,35 @@
         <v>3</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="K10" s="101">
+        <v>107</v>
+      </c>
+      <c r="K10" s="52">
         <v>2</v>
       </c>
-      <c r="L10" s="101" t="s">
-        <v>90</v>
-      </c>
-      <c r="M10" s="101">
+      <c r="L10" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="M10" s="52">
         <v>8</v>
       </c>
-      <c r="N10" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="O10" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P10" s="89" t="s">
-        <v>88</v>
+      <c r="N10" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P10" s="43" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
       <c r="D11" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G11" s="11">
         <v>4</v>
@@ -5131,35 +5050,35 @@
         <v>4</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="L11" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M11" s="130">
+        <v>111</v>
+      </c>
+      <c r="L11" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" s="70">
         <v>10</v>
       </c>
-      <c r="N11" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O11" s="118" t="s">
-        <v>87</v>
+      <c r="N11" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O11" s="53" t="s">
+        <v>80</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G12" s="11">
         <v>5</v>
@@ -5168,39 +5087,39 @@
         <v>5</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="L12" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" s="130">
+        <v>112</v>
+      </c>
+      <c r="L12" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="70">
         <v>11</v>
       </c>
-      <c r="N12" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12" s="118" t="s">
-        <v>87</v>
+      <c r="N12" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O12" s="53" t="s">
+        <v>80</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="50">
+      <c r="B13" s="149">
         <v>2</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>128</v>
+      <c r="C13" s="149" t="s">
+        <v>121</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G13" s="17">
         <v>6</v>
@@ -5209,27 +5128,27 @@
         <v>6</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="L13" s="18"/>
-      <c r="M13" s="131"/>
+      <c r="M13" s="71"/>
       <c r="N13" s="18"/>
       <c r="O13" s="18"/>
       <c r="P13" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G14" s="11">
         <v>7</v>
@@ -5238,35 +5157,35 @@
         <v>7</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K14" s="3">
         <v>1</v>
       </c>
-      <c r="L14" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="130">
+      <c r="L14" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14" s="70">
         <v>-0.01</v>
       </c>
-      <c r="N14" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O14" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P14" s="134" t="s">
-        <v>123</v>
+      <c r="N14" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O14" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P14" s="74" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
       <c r="D15" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G15" s="11">
         <v>8</v>
@@ -5275,72 +5194,72 @@
         <v>8</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K15" s="3">
         <v>1</v>
       </c>
-      <c r="L15" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15" s="130">
+      <c r="L15" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" s="70">
         <v>0</v>
       </c>
-      <c r="N15" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O15" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P15" s="134" t="s">
-        <v>123</v>
+      <c r="N15" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O15" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P15" s="74" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G16" s="11">
         <v>9</v>
       </c>
-      <c r="H16" s="93">
+      <c r="H16" s="47">
         <v>9</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K16" s="3">
         <v>1</v>
       </c>
-      <c r="L16" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M16" s="130">
+      <c r="L16" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="70">
         <v>0.01</v>
       </c>
-      <c r="N16" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O16" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P16" s="134" t="s">
-        <v>88</v>
+      <c r="N16" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" s="74" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
       <c r="D17" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G17" s="11">
         <v>10</v>
@@ -5349,35 +5268,35 @@
         <v>10</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K17" s="3">
         <v>1</v>
       </c>
-      <c r="L17" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M17" s="132">
+      <c r="L17" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="72">
         <v>9999.99</v>
       </c>
-      <c r="N17" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O17" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P17" s="134" t="s">
-        <v>88</v>
+      <c r="N17" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O17" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P17" s="74" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="125"/>
       <c r="D18" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G18" s="11">
         <v>11</v>
@@ -5386,70 +5305,70 @@
         <v>11</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J18" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K18" s="3">
         <v>1</v>
       </c>
-      <c r="L18" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M18" s="132">
+      <c r="L18" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M18" s="72">
         <v>10000</v>
       </c>
-      <c r="N18" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O18" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P18" s="134" t="s">
-        <v>123</v>
+      <c r="N18" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O18" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P18" s="74" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="50">
+      <c r="B19" s="149">
         <v>3</v>
       </c>
-      <c r="C19" s="54"/>
+      <c r="C19" s="157"/>
       <c r="D19" s="3"/>
       <c r="G19" s="11">
         <v>12</v>
       </c>
-      <c r="H19" s="93">
+      <c r="H19" s="47">
         <v>12</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K19" s="3">
         <v>1</v>
       </c>
-      <c r="L19" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="M19" s="132">
+      <c r="L19" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="M19" s="72">
         <v>10000.01</v>
       </c>
-      <c r="N19" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="O19" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="P19" s="134" t="s">
-        <v>123</v>
+      <c r="N19" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="O19" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="P19" s="74" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="156"/>
       <c r="D20" s="3"/>
       <c r="G20" s="11">
         <v>13</v>
@@ -5457,34 +5376,34 @@
       <c r="H20" s="13">
         <v>13</v>
       </c>
-      <c r="I20" s="161" t="s">
-        <v>48</v>
+      <c r="I20" s="90" t="s">
+        <v>41</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K20" s="3">
         <v>-1</v>
       </c>
-      <c r="L20" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="M20" s="129">
+      <c r="L20" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="M20" s="69">
         <v>10</v>
       </c>
-      <c r="N20" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="O20" s="116" t="s">
-        <v>87</v>
-      </c>
-      <c r="P20" s="133" t="s">
-        <v>117</v>
+      <c r="N20" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="O20" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="P20" s="73" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="156"/>
       <c r="D21" s="3"/>
       <c r="G21" s="11">
         <v>14</v>
@@ -5494,14 +5413,14 @@
       <c r="J21" s="21"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="132"/>
+      <c r="M21" s="72"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
+      <c r="B22" s="156"/>
+      <c r="C22" s="156"/>
       <c r="D22" s="3"/>
       <c r="G22" s="11">
         <v>15</v>
@@ -5511,14 +5430,14 @@
       <c r="J22" s="21"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
-      <c r="M22" s="132"/>
+      <c r="M22" s="72"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
       <c r="D23" s="3"/>
       <c r="G23" s="11">
         <v>16</v>
@@ -5528,14 +5447,14 @@
       <c r="J23" s="21"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
-      <c r="M23" s="132"/>
+      <c r="M23" s="72"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="3"/>
       <c r="G24" s="11">
         <v>17</v>
@@ -5545,20 +5464,20 @@
       <c r="J24" s="21"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="132"/>
+      <c r="M24" s="72"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="50">
+      <c r="B25" s="149">
         <v>4</v>
       </c>
-      <c r="C25" s="54" t="s">
-        <v>39</v>
+      <c r="C25" s="157" t="s">
+        <v>32</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G25" s="11">
         <v>18</v>
@@ -5568,58 +5487,58 @@
       <c r="J25" s="21"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="132"/>
+      <c r="M25" s="72"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
+      <c r="B26" s="156"/>
+      <c r="C26" s="156"/>
       <c r="D26" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
+      <c r="B27" s="156"/>
+      <c r="C27" s="156"/>
       <c r="D27" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
+      <c r="B28" s="156"/>
+      <c r="C28" s="156"/>
       <c r="D28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="51"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
+        <v>32</v>
+      </c>
+      <c r="G28" s="146"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
       <c r="N28" s="25"/>
     </row>
     <row r="29" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
       <c r="D29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="56"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
+        <v>32</v>
+      </c>
+      <c r="I29" s="159"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="131"/>
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="125"/>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6594,12 +6513,6 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="I29:M29"/>
@@ -6614,6 +6527,12 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6644,120 +6563,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="42"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="2" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="59"/>
+      <c r="B3" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="113"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="78" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="106" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="99" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
+      <c r="B4" s="114" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="118" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="120" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="76"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="76"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="115"/>
       <c r="F5" s="27" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="K5" s="73"/>
-      <c r="L5" s="137" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="137" t="s">
-        <v>55</v>
+        <v>30</v>
+      </c>
+      <c r="J5" s="126" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="127"/>
+      <c r="L5" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="28">
         <v>1</v>
       </c>
-      <c r="C6" s="80" t="s">
-        <v>56</v>
+      <c r="C6" s="132" t="s">
+        <v>49</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="101">
+        <v>51</v>
+      </c>
+      <c r="F6" s="52">
         <v>1</v>
       </c>
-      <c r="G6" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="101">
+      <c r="G6" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="52">
         <v>10</v>
       </c>
-      <c r="I6" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="97"/>
-      <c r="L6" s="143" t="s">
-        <v>88</v>
-      </c>
-      <c r="M6" s="144" t="s">
-        <v>88</v>
+      <c r="I6" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="99"/>
+      <c r="L6" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="81" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6765,34 +6684,34 @@
         <f t="shared" ref="B7:B24" si="0">B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="81"/>
+      <c r="C7" s="133"/>
       <c r="D7" s="30" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="101">
+        <v>51</v>
+      </c>
+      <c r="F7" s="52">
         <v>2</v>
       </c>
-      <c r="G7" s="101" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="101">
+      <c r="G7" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="52">
         <v>8</v>
       </c>
-      <c r="I7" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="97"/>
-      <c r="L7" s="145" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="146" t="s">
-        <v>88</v>
+      <c r="I7" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="99"/>
+      <c r="L7" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="83" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6800,34 +6719,34 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="139" t="s">
-        <v>59</v>
+      <c r="C8" s="133"/>
+      <c r="D8" s="77" t="s">
+        <v>52</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="104">
+        <v>51</v>
+      </c>
+      <c r="F8" s="55">
         <v>0</v>
       </c>
-      <c r="G8" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="104">
+      <c r="G8" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="55">
         <v>10</v>
       </c>
-      <c r="I8" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J8" s="105" t="s">
+      <c r="I8" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="99"/>
+      <c r="L8" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="97"/>
-      <c r="L8" s="145" t="s">
-        <v>94</v>
-      </c>
-      <c r="M8" s="147" t="s">
-        <v>94</v>
+      <c r="M8" s="84" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6835,34 +6754,34 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="139" t="s">
-        <v>132</v>
+      <c r="C9" s="133"/>
+      <c r="D9" s="77" t="s">
+        <v>125</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="95">
+        <v>51</v>
+      </c>
+      <c r="F9" s="49">
         <v>1</v>
       </c>
-      <c r="G9" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="95">
+      <c r="G9" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="49">
         <v>0</v>
       </c>
-      <c r="I9" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" s="97"/>
-      <c r="L9" s="145" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="147" t="s">
-        <v>97</v>
+      <c r="I9" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="99"/>
+      <c r="L9" s="82" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="84" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6870,128 +6789,128 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="139" t="s">
-        <v>60</v>
+      <c r="C10" s="133"/>
+      <c r="D10" s="77" t="s">
+        <v>53</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F10" s="16">
         <v>-3</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H10" s="16">
         <v>-34.200000000000003</v>
       </c>
-      <c r="I10" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="97"/>
-      <c r="L10" s="119" t="s">
-        <v>98</v>
-      </c>
-      <c r="M10" s="100"/>
+      <c r="I10" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="99"/>
+      <c r="L10" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="M10" s="51"/>
     </row>
     <row r="11" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="139" t="s">
-        <v>133</v>
+      <c r="C11" s="133"/>
+      <c r="D11" s="77" t="s">
+        <v>126</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F11" s="16">
         <v>1</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H11" s="16">
         <v>10000</v>
       </c>
-      <c r="I11" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="97"/>
-      <c r="L11" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="100"/>
+      <c r="I11" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="99"/>
+      <c r="L11" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="51"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="139" t="s">
-        <v>134</v>
+      <c r="C12" s="133"/>
+      <c r="D12" s="77" t="s">
+        <v>127</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F12" s="16">
         <v>-3</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H12" s="16">
         <v>10001</v>
       </c>
-      <c r="I12" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="97"/>
-      <c r="L12" s="119" t="s">
-        <v>98</v>
-      </c>
-      <c r="M12" s="100"/>
+      <c r="I12" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="99"/>
+      <c r="L12" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" s="51"/>
     </row>
     <row r="13" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="141" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="160">
+      <c r="C13" s="133"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="89">
         <v>1</v>
       </c>
-      <c r="G13" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="129">
+      <c r="G13" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="69">
         <v>9</v>
       </c>
-      <c r="I13" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" s="142"/>
-      <c r="L13" s="143" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="144" t="s">
-        <v>88</v>
+      <c r="I13" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="101"/>
+      <c r="L13" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="M13" s="81" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6999,64 +6918,64 @@
         <f>B12+1</f>
         <v>8</v>
       </c>
-      <c r="C14" s="81"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="141" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="104">
+        <v>51</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="55">
         <v>0</v>
       </c>
-      <c r="G14" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="129">
+      <c r="G14" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="69">
         <v>10</v>
       </c>
-      <c r="I14" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="117" t="s">
+      <c r="I14" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="101"/>
+      <c r="L14" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="142"/>
-      <c r="L14" s="145" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="147" t="s">
-        <v>94</v>
+      <c r="M14" s="84" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11"/>
-      <c r="C15" s="81"/>
+      <c r="C15" s="133"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="141" t="s">
-        <v>145</v>
-      </c>
-      <c r="F15" s="163">
+      <c r="E15" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="F15" s="92">
         <v>-1</v>
       </c>
-      <c r="G15" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="129">
+      <c r="G15" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="69">
         <v>11</v>
       </c>
-      <c r="I15" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="117" t="s">
+      <c r="I15" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="101"/>
+      <c r="L15" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="K15" s="142"/>
-      <c r="L15" s="145" t="s">
-        <v>94</v>
-      </c>
-      <c r="M15" s="147" t="s">
-        <v>94</v>
+      <c r="M15" s="84" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7064,100 +6983,100 @@
         <f>B14+1</f>
         <v>9</v>
       </c>
-      <c r="C16" s="81"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="141" t="s">
-        <v>62</v>
+        <v>51</v>
+      </c>
+      <c r="E16" s="79" t="s">
+        <v>55</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="130">
+        <v>111</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="70">
         <v>10</v>
       </c>
-      <c r="I16" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="K16" s="149"/>
-      <c r="L16" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="100"/>
+      <c r="I16" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="103"/>
+      <c r="L16" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" s="51"/>
     </row>
     <row r="17" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C17" s="81"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="141" t="s">
-        <v>63</v>
+        <v>51</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>56</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="130">
+        <v>112</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="70">
         <v>11</v>
       </c>
-      <c r="I17" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="150" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="151"/>
-      <c r="L17" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="100"/>
+      <c r="I17" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17" s="104" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="105"/>
+      <c r="L17" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="M17" s="51"/>
     </row>
     <row r="18" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C18" s="81"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="141" t="s">
-        <v>135</v>
+        <v>51</v>
+      </c>
+      <c r="E18" s="79" t="s">
+        <v>128</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
-      <c r="G18" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="130">
+      <c r="G18" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="70">
         <v>-0.01</v>
       </c>
-      <c r="I18" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="152" t="s">
-        <v>87</v>
-      </c>
-      <c r="K18" s="154"/>
-      <c r="L18" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="M18" s="147" t="s">
-        <v>97</v>
+      <c r="I18" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="107"/>
+      <c r="L18" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" s="84" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7165,34 +7084,34 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C19" s="81"/>
+      <c r="C19" s="133"/>
       <c r="D19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="141" t="s">
-        <v>136</v>
+        <v>51</v>
+      </c>
+      <c r="E19" s="79" t="s">
+        <v>129</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
       </c>
-      <c r="G19" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="130">
+      <c r="G19" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="70">
         <v>0</v>
       </c>
-      <c r="I19" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="152" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="154"/>
-      <c r="L19" s="147" t="s">
-        <v>97</v>
-      </c>
-      <c r="M19" s="147" t="s">
-        <v>97</v>
+      <c r="I19" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="107"/>
+      <c r="L19" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="M19" s="84" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7200,34 +7119,34 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C20" s="81"/>
+      <c r="C20" s="133"/>
       <c r="D20" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="141" t="s">
-        <v>137</v>
+        <v>51</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>130</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
       </c>
-      <c r="G20" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H20" s="130">
+      <c r="G20" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="70">
         <v>0.01</v>
       </c>
-      <c r="I20" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J20" s="152" t="s">
-        <v>87</v>
-      </c>
-      <c r="K20" s="154"/>
-      <c r="L20" s="156" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" s="156" t="s">
-        <v>88</v>
+      <c r="I20" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="107"/>
+      <c r="L20" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="86" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7235,120 +7154,120 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C21" s="81"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="141" t="s">
-        <v>138</v>
+        <v>51</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>131</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
       </c>
-      <c r="G21" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H21" s="132">
+      <c r="G21" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="72">
         <v>9999.99</v>
       </c>
-      <c r="I21" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J21" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="159"/>
-      <c r="L21" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="M21" s="100"/>
+      <c r="I21" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="108"/>
+      <c r="L21" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="M21" s="51"/>
     </row>
     <row r="22" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
-      <c r="C22" s="81"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="11"/>
-      <c r="E22" s="141" t="s">
-        <v>139</v>
+      <c r="E22" s="79" t="s">
+        <v>132</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
-      <c r="G22" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" s="132">
+      <c r="G22" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="72">
         <v>10000</v>
       </c>
-      <c r="I22" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J22" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="K22" s="159"/>
-      <c r="L22" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="M22" s="100"/>
+      <c r="I22" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J22" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="108"/>
+      <c r="L22" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="M22" s="51"/>
     </row>
     <row r="23" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <f>B21+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="81"/>
+      <c r="C23" s="133"/>
       <c r="D23" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="141" t="s">
-        <v>140</v>
+        <v>51</v>
+      </c>
+      <c r="E23" s="79" t="s">
+        <v>133</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
       </c>
-      <c r="G23" s="101" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="132">
+      <c r="G23" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="72">
         <v>10000.01</v>
       </c>
-      <c r="I23" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="148" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="159"/>
-      <c r="L23" s="119" t="s">
-        <v>97</v>
-      </c>
-      <c r="M23" s="100"/>
+      <c r="I23" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="108"/>
+      <c r="L23" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="M23" s="51"/>
     </row>
     <row r="24" spans="2:16" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="77"/>
+      <c r="C24" s="117"/>
       <c r="D24" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="157" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="158" t="s">
-        <v>120</v>
+        <v>51</v>
+      </c>
+      <c r="E24" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="88" t="s">
+        <v>113</v>
       </c>
       <c r="G24" s="27"/>
-      <c r="H24" s="138"/>
+      <c r="H24" s="76"/>
       <c r="I24" s="27"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="155"/>
-      <c r="L24" s="140" t="s">
-        <v>142</v>
-      </c>
-      <c r="M24" s="140" t="s">
-        <v>143</v>
+      <c r="J24" s="126"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="M24" s="78" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="2:16" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -7368,7 +7287,7 @@
     </row>
     <row r="26" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="31" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
@@ -7378,102 +7297,102 @@
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
       <c r="J26" s="32"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="45"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="131"/>
       <c r="M26" s="32"/>
     </row>
     <row r="27" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M27" s="32"/>
     </row>
     <row r="28" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="135" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="137"/>
+      <c r="M28" s="135" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="136"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="137"/>
+    </row>
+    <row r="29" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="121" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="114" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="114" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="33" t="s">
+      <c r="G29" s="138" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="66" t="s">
+      <c r="H29" s="140" t="s">
         <v>67</v>
       </c>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="66" t="s">
+      <c r="I29" s="113"/>
+      <c r="J29" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="68"/>
-    </row>
-    <row r="29" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="71" t="s">
+      <c r="L29" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="M29" s="143" t="s">
+        <v>67</v>
+      </c>
+      <c r="N29" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="O29" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="P29" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="82" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="I29" s="59"/>
-      <c r="J29" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="K29" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="L29" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="M29" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="N29" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="O29" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="P29" s="62" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="30" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="70"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="63"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="124"/>
+      <c r="N30" s="125"/>
+      <c r="O30" s="125"/>
+      <c r="P30" s="134"/>
     </row>
     <row r="31" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="34" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C31" s="35">
         <v>10</v>
@@ -7488,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="38"/>
-      <c r="H31" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="I31" s="42"/>
+      <c r="H31" s="93" t="s">
+        <v>72</v>
+      </c>
+      <c r="I31" s="94"/>
       <c r="J31" s="3">
         <v>3</v>
       </c>
@@ -7502,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="39" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="N31" s="3">
         <v>5</v>
@@ -8498,6 +8417,38 @@
     <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="C6:C24"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="F4:K4"/>
     <mergeCell ref="L4:N4"/>
@@ -8513,39 +8464,7 @@
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J15:K15"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="C6:C24"/>
     <mergeCell ref="N29:N30"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="H28:L28"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="M29:M30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
